--- a/data/trans_dic/P1438_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1438_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,34</t>
+          <t>1,45; 4,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,83</t>
+          <t>1,98; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,28</t>
+          <t>2,04; 4,21</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,02</t>
+          <t>2,92; 7,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,62</t>
+          <t>5,68; 9,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,45</t>
+          <t>4,78; 7,7</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 12,83</t>
+          <t>7,34; 12,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,36; 20,68</t>
+          <t>13,85; 19,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 15,86</t>
+          <t>11,7; 15,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,14</t>
+          <t>2,75; 7,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,26</t>
+          <t>5,81; 9,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,24</t>
+          <t>4,8; 7,88</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,3</t>
+          <t>2,01; 6,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,63</t>
+          <t>6,14; 11,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,45</t>
+          <t>4,72; 8,14</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,71</t>
+          <t>10,63; 17,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,58; 23,58</t>
+          <t>16,15; 23,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,42; 19,31</t>
+          <t>14,25; 19,04</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,63</t>
+          <t>2,17; 4,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,01</t>
+          <t>7,2; 10,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,16</t>
+          <t>5,13; 7,49</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,31</t>
+          <t>1,03; 2,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,76</t>
+          <t>3,41; 5,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,58</t>
+          <t>2,47; 4,0</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,16</t>
+          <t>4,03; 5,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,38; 8,83</t>
+          <t>7,92; 9,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,38; 6,82</t>
+          <t>6,17; 7,15</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>18851</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4393; 16618</t>
+          <t>4621; 15468</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5629; 13986</t>
+          <t>6248; 15293</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12395; 25737</t>
+          <t>12959; 26710</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>40479</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61857</t>
+          <t>65552</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13955; 36326</t>
+          <t>15470; 37433</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29283; 49465</t>
+          <t>31000; 52597</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47710; 76810</t>
+          <t>51461; 82792</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>31147</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59539</t>
+          <t>60252</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89950</t>
+          <t>91399</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22125; 40535</t>
+          <t>23189; 40718</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50146; 72197</t>
+          <t>49376; 71176</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77136; 105493</t>
+          <t>78691; 105829</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43619</t>
+          <t>49320</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9484; 25446</t>
+          <t>10272; 28586</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16690; 39304</t>
+          <t>24536; 41308</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30139; 57085</t>
+          <t>38200; 62675</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>26681</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3652; 11266</t>
+          <t>4128; 12840</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13527; 24217</t>
+          <t>13937; 25081</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19101; 32686</t>
+          <t>20412; 35206</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50839</t>
+          <t>51662</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87065</t>
+          <t>88076</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28283; 45059</t>
+          <t>28763; 46213</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42507; 60461</t>
+          <t>42499; 61028</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75839; 101575</t>
+          <t>76058; 101663</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>23763</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>67334</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72189</t>
+          <t>91097</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12046; 28806</t>
+          <t>15554; 34727</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23563; 76452</t>
+          <t>55493; 81695</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46384; 90662</t>
+          <t>76311; 111380</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>32118</t>
+          <t>36988</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44531</t>
+          <t>51089</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4379; 21407</t>
+          <t>8240; 22849</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25042; 41185</t>
+          <t>28337; 47910</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27576; 58916</t>
+          <t>40199; 65199</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>163729</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>289340</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>442068</t>
+          <t>482063</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>118186; 178489</t>
+          <t>142231; 187382</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>233275; 322918</t>
+          <t>295366; 346789</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>382468; 485284</t>
+          <t>448195; 519194</t>
         </is>
       </c>
     </row>
